--- a/artfynd/A 52858-2023 artfynd.xlsx
+++ b/artfynd/A 52858-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52858-2023 artfynd.xlsx
+++ b/artfynd/A 52858-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -957,6 +957,134 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121930461</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57363</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vadsbro Ekskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590344</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6537427</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52858-2023 artfynd.xlsx
+++ b/artfynd/A 52858-2023 artfynd.xlsx
@@ -962,7 +962,7 @@
         <v>121930461</v>
       </c>
       <c r="B4" t="n">
-        <v>57363</v>
+        <v>57371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 52858-2023 artfynd.xlsx
+++ b/artfynd/A 52858-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>80004323</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590463.2052633149</v>
+        <v>590463</v>
       </c>
       <c r="R2" t="n">
-        <v>6537299.484154586</v>
+        <v>6537299</v>
       </c>
       <c r="S2" t="n">
         <v>7</v>
@@ -820,12 +815,7 @@
         <v>85448984</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -867,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590404.0473739082</v>
+        <v>590404</v>
       </c>
       <c r="R3" t="n">
-        <v>6537397.657279149</v>
+        <v>6537398</v>
       </c>
       <c r="S3" t="n">
         <v>14</v>
@@ -900,19 +890,9 @@
           <t>2020-05-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-05-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -962,12 +942,7 @@
         <v>121930461</v>
       </c>
       <c r="B4" t="n">
-        <v>57380</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52858-2023 artfynd.xlsx
+++ b/artfynd/A 52858-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -809,6 +814,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80004323</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -936,6 +946,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85448984</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1059,8 +1074,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121930461</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>